--- a/data/trans_dic/P1432-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1432-Clase-trans_dic.xlsx
@@ -678,37 +678,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,5</t>
+          <t>0,21; 2,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,31</t>
+          <t>0,3; 2,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,66</t>
+          <t>0,23; 1,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,43</t>
+          <t>0,13; 1,42</t>
         </is>
       </c>
     </row>
@@ -788,22 +788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,8</t>
+          <t>0,48; 2,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,89</t>
+          <t>0,28; 2,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,99</t>
+          <t>0,28; 3,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,14</t>
+          <t>0,53; 2,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,04</t>
+          <t>0,29; 2,14</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,49</t>
+          <t>0,35; 2,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,89</t>
+          <t>0,49; 2,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,89</t>
+          <t>0,15; 1,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,11</t>
+          <t>0,36; 3,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,37</t>
+          <t>0,54; 2,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,17</t>
+          <t>0,58; 2,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,93</t>
+          <t>0,33; 1,85</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,06</t>
+          <t>0,77; 2,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,61</t>
+          <t>0,36; 1,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,85</t>
+          <t>0,15; 0,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,67</t>
+          <t>0,28; 1,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,57</t>
+          <t>0,25; 1,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,13</t>
+          <t>0,5; 2,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,61</t>
+          <t>0,75; 1,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,33</t>
+          <t>0,43; 1,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,15</t>
+          <t>0,39; 1,17</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,76</t>
+          <t>0,52; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,54</t>
+          <t>0,2; 1,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,96</t>
+          <t>0,4; 1,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,49</t>
+          <t>0,95; 3,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,31</t>
+          <t>1,69; 4,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,11</t>
+          <t>0,46; 2,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,71</t>
+          <t>0,96; 2,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,93</t>
+          <t>1,23; 2,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,75</t>
+          <t>0,59; 1,62</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1243,32 +1243,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,06</t>
+          <t>1,35; 3,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,39</t>
+          <t>1,45; 3,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,46</t>
+          <t>1,48; 3,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,58</t>
+          <t>1,1; 2,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,74</t>
+          <t>1,2; 2,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,74</t>
+          <t>1,12; 2,69</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,5</t>
+          <t>0,79; 1,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,99</t>
+          <t>0,39; 1,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,8</t>
+          <t>0,32; 0,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,93</t>
+          <t>1,09; 1,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,12</t>
+          <t>1,24; 2,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,92</t>
+          <t>1,05; 1,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,61</t>
+          <t>1,04; 1,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,46</t>
+          <t>0,92; 1,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,28</t>
+          <t>0,76; 1,26</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1007; 11829</t>
+          <t>983; 10876</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4801</t>
+          <t>0; 4742</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5942</t>
+          <t>0; 5604</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4747</t>
+          <t>0; 4342</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>980; 10417</t>
+          <t>957; 8211</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 8556</t>
+          <t>0; 7549</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1822; 12960</t>
+          <t>1814; 12293</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1089; 10382</t>
+          <t>1038; 10374</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1256; 11078</t>
+          <t>992; 10994</t>
         </is>
       </c>
     </row>
@@ -1802,22 +1802,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1732; 10264</t>
+          <t>1751; 10189</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5229</t>
+          <t>0; 6170</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5917</t>
+          <t>0; 6291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1019; 10756</t>
+          <t>1035; 11083</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1050; 14839</t>
+          <t>1053; 13703</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3746; 15832</t>
+          <t>3926; 15699</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5183</t>
+          <t>0; 5170</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2247; 15316</t>
+          <t>2210; 16019</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2068; 13492</t>
+          <t>1888; 12524</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3107; 18209</t>
+          <t>3077; 16981</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>777; 9844</t>
+          <t>782; 10199</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 7863</t>
+          <t>0; 8073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>940; 8077</t>
+          <t>940; 8157</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 8185</t>
+          <t>0; 7197</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3930; 16843</t>
+          <t>3827; 16619</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4944; 19269</t>
+          <t>5149; 20010</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2179; 13288</t>
+          <t>2251; 12744</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10065; 25536</t>
+          <t>9510; 25385</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5041; 18657</t>
+          <t>4135; 19398</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1645; 9762</t>
+          <t>1739; 9665</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2165; 11947</t>
+          <t>2033; 11685</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1960; 11975</t>
+          <t>1944; 11192</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3880; 17616</t>
+          <t>4138; 16723</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13414; 31505</t>
+          <t>14688; 32855</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8480; 25658</t>
+          <t>8243; 25412</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7442; 22778</t>
+          <t>7608; 23101</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1668; 9660</t>
+          <t>1834; 9806</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1009; 7841</t>
+          <t>1010; 8363</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2569; 12175</t>
+          <t>2482; 11112</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5562; 19846</t>
+          <t>5392; 20001</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13597; 32795</t>
+          <t>12886; 31126</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3221; 15601</t>
+          <t>3372; 15474</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9208; 24932</t>
+          <t>8832; 25598</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16964; 37230</t>
+          <t>15601; 36059</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7942; 23748</t>
+          <t>8058; 22048</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2469,32 +2469,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16689; 38258</t>
+          <t>16917; 38133</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16142; 37518</t>
+          <t>16085; 37462</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15717; 37404</t>
+          <t>15967; 36671</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17483; 39837</t>
+          <t>17093; 37991</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16224; 37699</t>
+          <t>16529; 38310</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16422; 37450</t>
+          <t>15331; 36873</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25256; 49162</t>
+          <t>25839; 49629</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13985; 33761</t>
+          <t>13302; 36156</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10209; 27170</t>
+          <t>10711; 27533</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36860; 65059</t>
+          <t>36718; 65441</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>43163; 75162</t>
+          <t>43906; 75805</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36903; 67667</t>
+          <t>37076; 67696</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>67844; 107173</t>
+          <t>69098; 108864</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>63593; 102076</t>
+          <t>64399; 101261</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52118; 88862</t>
+          <t>52589; 87031</t>
         </is>
       </c>
     </row>
